--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(3).xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity Projects\VNovelizerTest_v1.0\Assets\Resources\VNovelizerRes\ExcelVNScripts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17415" windowHeight="7680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线313-315（中下）" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="436">
   <si>
     <t>ID</t>
   </si>
@@ -211,72 +216,75 @@
     <t>你转过身，按下录音机上的一个按钮，只听“啪嗒”一声，整盘磁带如尸体般滑了出来，被你轻捏在掌心。</t>
   </si>
   <si>
+    <t>parallel(playsfx(Kata);bgfade(sntzm_david313-315(3)_10,1))</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=8</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>它摸起来凉飕飕的，像一块冻了数十年的冷硬的石头。磁带中间竖着一道凹陷的口子，似是被什么尖锐的利物刺出的伤痕。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=9</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>裂口旁，一个歪歪扭扭的大写的L在手电的寒光下清晰可见。当大卫的目光在这道粗糙的字迹上扫过时，那双赤红的瞳孔再一次不受控制地收紧了。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=10</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>你不敢有丝毫耽搁，将它收进裤包便扭头看向外面的走廊。诡谲的光依旧在那只飞蛾身上持续不断地闪烁着，如同深海中若隐若现的信号灯，没人知道它后面藏着的是美丽的珊瑚还是鲨鱼的血口。</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_david313-315(3)_13,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=11</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>我们走吧。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=12</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>你率先迈开步子，以光为刃劈开周围的黑暗，沿着地上的血脚印朝B3-15号病房走去。</t>
+  </si>
+  <si>
+    <t>jump(21)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=13; gotomainline=21</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>你没有看他，只是兀自按下录音机上的某个开关。随着你的动作，那盘记录着罪证的磁带“啪嗒”一声弹了出来，像从巨兽肠道里挖出来的一具腐坏的尸体。</t>
+  </si>
+  <si>
     <t>bgfade(sntzm_david313-315(3)_10,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=8</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>它摸起来凉飕飕的，像一块冻了数十年的冷硬的石头。磁带中间竖着一道凹陷的口子，似是被什么尖锐的利物刺出的伤痕。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=9</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>裂口旁，一个歪歪扭扭的大写的L在手电的寒光下清晰可见。当大卫的目光在这道粗糙的字迹上扫过时，那双赤红的瞳孔再一次不受控制地收紧了。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=10</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>你不敢有丝毫耽搁，将它收进裤包便扭头看向外面的走廊。诡谲的光依旧在那只飞蛾身上持续不断地闪烁着，如同深海中若隐若现的信号灯，没人知道它后面藏着的是美丽的珊瑚还是鲨鱼的血口。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_david313-315(3)_13,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=11</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>我们走吧。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=12</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>你率先迈开步子，以光为刃劈开周围的黑暗，沿着地上的血脚印朝B3-15号病房走去。</t>
-  </si>
-  <si>
-    <t>jump(21)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=13; gotomainline=21</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>你没有看他，只是兀自按下录音机上的某个开关。随着你的动作，那盘记录着罪证的磁带“啪嗒”一声弹了出来，像从巨兽肠道里挖出来的一具腐坏的尸体。</t>
-  </si>
-  <si>
     <t>源类型=type:txt_pb; 层级=3; tag=沉默</t>
   </si>
   <si>
@@ -550,7 +558,7 @@
     <t>49</t>
   </si>
   <si>
-    <t>大卫眼神一暗，但还是鼓起勇气，伸手揭开了它的封面。扉页上贴着一张有些泛黄的一寸照片，不是自己......而是一个完全陌生的女人。大卫眼神一暗，但还是鼓起勇气，伸手揭开了它的封面。扉页上贴着一张有些泛黄</t>
+    <t>大卫眼神一暗，但还是鼓起勇气，伸手揭开了它的封面。扉页上贴着一张有些泛黄的一寸照片，不是自己......而是一个完全陌生的女人。</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=33</t>
@@ -562,6 +570,9 @@
     <t>她留着一头利落的长发，嘴角抿成一道锋利的直线，一双和某人极其相似的绿眼睛，正隔着十余年的光阴，与他隔空相望。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=34</t>
   </si>
   <si>
@@ -589,6 +600,9 @@
     <t>他难以置信地看着你，视线在你和照片上的女性之间来回游移，仿佛正确认你是否又一次陷入了那危险的幻觉。</t>
   </si>
   <si>
+    <t>11 enhanced the_mountain-hope-background</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=37</t>
   </si>
   <si>
@@ -697,10 +711,13 @@
     <t>65</t>
   </si>
   <si>
-    <t>大卫注视着眼前诡异到渗人的一幕，一直警戒在身后的枪口跟着垂下了半寸，他想起一件事情，原本有些犹豫，是否应该立刻告知你。但当同样令人不安的现象发生在你至亲的遗物上时，那份如蛆附骨的不安终于促使他开口打破</t>
+    <t>大卫注视着眼前诡异到渗人的一幕，一直警戒在身后的枪口跟着垂下了半寸，他想起一件事情，原本有些犹豫，是否应该立刻告知你。</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=49</t>
+  </si>
+  <si>
+    <t>但当同样令人不安的现象发生在你至亲的遗物上时，那份如蛆附骨的不安终于促使他开口打破沉默。</t>
   </si>
   <si>
     <t>66</t>
@@ -2591,7 +2608,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3244,15 +3261,15 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="55.5" spans="1:12">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3270,7 +3287,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3285,12 +3302,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" ht="55.5" spans="1:12">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3308,7 +3325,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3328,7 +3345,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
@@ -3346,7 +3363,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3361,12 +3378,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" ht="42" spans="1:12">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3384,7 +3401,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3404,7 +3421,7 @@
     </row>
     <row r="22" ht="54" spans="1:12">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3422,7 +3439,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3442,7 +3459,7 @@
     </row>
     <row r="23" ht="27" spans="1:12">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3460,7 +3477,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3480,7 +3497,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3510,15 +3527,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:12">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3536,7 +3553,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3551,12 +3568,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" ht="30" spans="1:12">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
@@ -3574,7 +3591,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3589,12 +3606,12 @@
         <v>39</v>
       </c>
       <c r="L26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" ht="43.5" spans="1:12">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3612,7 +3629,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3624,12 +3641,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
         <v>29</v>
@@ -3647,7 +3664,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3662,12 +3679,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" ht="55.5" spans="1:12">
       <c r="A29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3685,7 +3702,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3700,12 +3717,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" ht="40.5" spans="1:12">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3723,7 +3740,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3738,12 +3755,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" ht="40.5" spans="1:12">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3761,7 +3778,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3776,12 +3793,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:12">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3799,7 +3816,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3814,12 +3831,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" ht="40.5" spans="1:12">
       <c r="A33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3837,7 +3854,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3852,12 +3869,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" ht="55.5" spans="1:12">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3875,7 +3892,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3887,12 +3904,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" ht="67.5" spans="1:12">
       <c r="A35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3910,7 +3927,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3922,15 +3939,15 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B36" t="s">
         <v>36</v>
@@ -3948,7 +3965,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3963,12 +3980,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" ht="67.5" spans="1:12">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3986,7 +4003,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3998,15 +4015,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" ht="30" spans="1:12">
       <c r="A38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B38" t="s">
         <v>36</v>
@@ -4024,7 +4041,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4039,12 +4056,12 @@
         <v>39</v>
       </c>
       <c r="L38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" ht="30" spans="1:12">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4077,12 +4094,12 @@
         <v>43</v>
       </c>
       <c r="L39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" ht="90" spans="1:12">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4100,7 +4117,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4112,15 +4129,15 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" ht="90" spans="1:12">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4138,7 +4155,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4153,12 +4170,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" ht="57" spans="1:12">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4176,7 +4193,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4191,12 +4208,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" ht="27" spans="1:12">
       <c r="A43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4214,7 +4231,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4229,12 +4246,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" ht="27" spans="1:12">
       <c r="A44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4252,7 +4269,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4264,15 +4281,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" ht="27" spans="1:12">
       <c r="A45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4290,7 +4307,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4305,12 +4322,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" ht="30" spans="1:12">
       <c r="A46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B46" t="s">
         <v>36</v>
@@ -4328,7 +4345,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4343,12 +4360,12 @@
         <v>39</v>
       </c>
       <c r="L46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" ht="43.5" spans="1:12">
       <c r="A47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4366,7 +4383,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4381,12 +4398,12 @@
         <v>43</v>
       </c>
       <c r="L47" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="48" ht="69" spans="1:12">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" ht="42" spans="1:12">
       <c r="A48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4404,14 +4421,11 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
       </c>
-      <c r="I48" t="s">
-        <v>15</v>
-      </c>
       <c r="J48" t="s">
         <v>15</v>
       </c>
@@ -4419,12 +4433,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4442,13 +4456,13 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
       </c>
       <c r="I49" t="s">
-        <v>15</v>
+        <v>165</v>
       </c>
       <c r="J49" t="s">
         <v>15</v>
@@ -4457,12 +4471,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B50" t="s">
         <v>29</v>
@@ -4480,7 +4494,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4495,12 +4509,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4518,7 +4532,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4533,12 +4547,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="52" ht="40.5" spans="1:12">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="52" ht="45" spans="1:12">
       <c r="A52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4556,13 +4570,13 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
       </c>
       <c r="I52" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="J52" t="s">
         <v>15</v>
@@ -4571,12 +4585,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" ht="30" spans="1:12">
       <c r="A53" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s">
         <v>36</v>
@@ -4594,7 +4608,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4609,12 +4623,12 @@
         <v>39</v>
       </c>
       <c r="L53" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" ht="54" spans="1:12">
       <c r="A54" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4632,7 +4646,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4647,12 +4661,12 @@
         <v>43</v>
       </c>
       <c r="L54" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" ht="27" spans="1:12">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4670,7 +4684,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4685,12 +4699,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4708,7 +4722,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4723,12 +4737,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" ht="70.5" spans="1:12">
       <c r="A57" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4746,7 +4760,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4761,12 +4775,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" ht="27" spans="1:12">
       <c r="A58" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4784,7 +4798,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4799,12 +4813,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B59" t="s">
         <v>36</v>
@@ -4822,7 +4836,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4837,12 +4851,12 @@
         <v>39</v>
       </c>
       <c r="L59" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" ht="67.5" spans="1:12">
       <c r="A60" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4860,7 +4874,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4875,12 +4889,12 @@
         <v>43</v>
       </c>
       <c r="L60" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B61" t="s">
         <v>29</v>
@@ -4898,7 +4912,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4913,12 +4927,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="62" ht="69" spans="1:12">
       <c r="A62" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4936,7 +4950,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -4951,12 +4965,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" ht="67.5" spans="1:12">
       <c r="A63" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -4974,7 +4988,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -4986,15 +5000,15 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L63" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="64" ht="67.5" spans="1:12">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" ht="40.5" spans="1:12">
       <c r="A64" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5012,7 +5026,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5027,21 +5041,21 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="65" ht="30" spans="1:12">
-      <c r="A65" t="s">
-        <v>211</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="65" ht="40.5" spans="1:12">
+      <c r="A65">
+        <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -5049,8 +5063,8 @@
       <c r="F65" t="s">
         <v>15</v>
       </c>
-      <c r="G65" t="s">
-        <v>212</v>
+      <c r="G65" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5062,18 +5076,18 @@
         <v>15</v>
       </c>
       <c r="K65" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="L65" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="66" ht="54" spans="1:12">
+    <row r="66" ht="30" spans="1:12">
       <c r="A66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -5088,7 +5102,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5100,13 +5114,13 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>216</v>
+        <v>39</v>
       </c>
       <c r="L66" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="67" ht="57" spans="1:12">
+    <row r="67" ht="54" spans="1:12">
       <c r="A67" t="s">
         <v>218</v>
       </c>
@@ -5117,7 +5131,7 @@
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
@@ -5138,15 +5152,15 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>15</v>
+        <v>220</v>
       </c>
       <c r="L67" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="68" ht="58.5" spans="1:12">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" ht="57" spans="1:12">
       <c r="A68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5164,7 +5178,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5179,21 +5193,21 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="69" ht="40.5" spans="1:12">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="69" ht="58.5" spans="1:12">
       <c r="A69" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B69" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -5202,7 +5216,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5214,18 +5228,18 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" ht="40.5" spans="1:12">
       <c r="A70" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -5240,7 +5254,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5252,15 +5266,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L70" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="71" ht="40.5" spans="1:12">
       <c r="A71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5269,7 +5283,7 @@
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -5278,7 +5292,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5290,24 +5304,24 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="L71" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="72" ht="54" spans="1:12">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B72" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -5316,7 +5330,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5328,18 +5342,18 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="73" ht="54" spans="1:12">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -5354,7 +5368,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5366,15 +5380,15 @@
         <v>15</v>
       </c>
       <c r="K73" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L73" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="74" ht="69" spans="1:12">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="74" ht="54" spans="1:12">
       <c r="A74" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5383,7 +5397,7 @@
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -5392,7 +5406,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5404,15 +5418,15 @@
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="L74" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="75" ht="67.5" spans="1:12">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="75" ht="69" spans="1:12">
       <c r="A75" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5430,7 +5444,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5445,12 +5459,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="76" ht="40.5" spans="1:12">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="76" ht="67.5" spans="1:12">
       <c r="A76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5468,7 +5482,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5479,14 +5493,14 @@
       <c r="J76" t="s">
         <v>15</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>247</v>
+      <c r="K76" t="s">
+        <v>15</v>
       </c>
       <c r="L76" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="77" ht="90" spans="1:12">
+    <row r="77" ht="40.5" spans="1:12">
       <c r="A77" t="s">
         <v>249</v>
       </c>
@@ -5517,25 +5531,25 @@
       <c r="J77" t="s">
         <v>15</v>
       </c>
-      <c r="K77" t="s">
-        <v>15</v>
+      <c r="K77" s="3" t="s">
+        <v>251</v>
       </c>
       <c r="L77" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="78" ht="30" spans="1:12">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="78" ht="90" spans="1:12">
       <c r="A78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B78" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -5544,7 +5558,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5556,10 +5570,48 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>254</v>
+        <v>15</v>
       </c>
       <c r="L78" t="s">
         <v>255</v>
+      </c>
+    </row>
+    <row r="79" ht="30" spans="1:12">
+      <c r="A79" t="s">
+        <v>256</v>
+      </c>
+      <c r="B79" t="s">
+        <v>36</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>37</v>
+      </c>
+      <c r="E79" t="s">
+        <v>15</v>
+      </c>
+      <c r="F79" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" t="s">
+        <v>257</v>
+      </c>
+      <c r="H79" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" t="s">
+        <v>15</v>
+      </c>
+      <c r="J79" t="s">
+        <v>15</v>
+      </c>
+      <c r="K79" t="s">
+        <v>258</v>
+      </c>
+      <c r="L79" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -5580,39 +5632,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5620,7 +5672,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -5628,7 +5680,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5636,66 +5688,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B10" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B12" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B14" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B15" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -5717,616 +5769,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F5" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B6" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C6" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D6" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F6" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B7" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C7" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D7" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E7" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F7" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B8" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C8" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D8" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E8" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F8" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B9" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C9" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D9" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E9" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F9" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B10" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C10" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D10" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E10" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F10" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B11" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C11" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D11" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E11" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F11" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B12" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C12" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D12" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E12" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F12" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B13" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D13" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E13" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F13" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B14" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C14" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D14" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E14" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F14" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B15" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C15" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D15" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E15" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F15" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B16" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C16" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D16" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E16" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F16" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B17" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C17" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D17" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E17" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F17" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B18" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C18" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D18" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E18" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F18" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B19" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C19" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D19" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E19" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F19" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B20" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C20" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D20" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E20" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F20" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B21" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C21" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D21" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E21" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F21" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B22" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C22" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D22" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E22" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F22" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B23" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C23" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D23" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E23" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F23" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B24" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C24" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D24" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E24" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F24" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B25" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C25" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D25" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E25" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F25" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B26" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C26" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D26" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E26" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F26" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B27" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C27" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D27" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E27" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F27" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B28" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C28" t="s">
+        <v>419</v>
+      </c>
+      <c r="D28" t="s">
         <v>415</v>
       </c>
-      <c r="D28" t="s">
-        <v>411</v>
-      </c>
       <c r="E28" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F28" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B29" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C29" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D29" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E29" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F29" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B30" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C30" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D30" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E30" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F30" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B31" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C31" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D31" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线313-315（中下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="437">
   <si>
     <t>ID</t>
   </si>
@@ -486,7 +486,54 @@
     <t>jump(43)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=26; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"追问","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"0","dowlist4":[]}]}]}; gotomainline=43</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=26; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>追问</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=43</t>
+    </r>
   </si>
   <si>
     <t>42</t>
@@ -601,6 +648,9 @@
   </si>
   <si>
     <t>11 enhanced the_mountain-hope-background</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music11)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=37</t>
@@ -850,7 +900,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>, 1)</t>
+      <t>, 1)&amp;unlockscene(scene5)</t>
     </r>
   </si>
   <si>
@@ -4131,7 +4181,7 @@
       <c r="K40" t="s">
         <v>136</v>
       </c>
-      <c r="L40" t="s">
+      <c r="L40" s="2" t="s">
         <v>137</v>
       </c>
     </row>
@@ -4582,15 +4632,15 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="L52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" ht="30" spans="1:12">
       <c r="A53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B53" t="s">
         <v>36</v>
@@ -4608,7 +4658,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4623,12 +4673,12 @@
         <v>39</v>
       </c>
       <c r="L53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54" ht="54" spans="1:12">
       <c r="A54" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4646,7 +4696,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4661,12 +4711,12 @@
         <v>43</v>
       </c>
       <c r="L54" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" ht="27" spans="1:12">
       <c r="A55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4684,7 +4734,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4699,12 +4749,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4722,7 +4772,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4737,12 +4787,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" ht="70.5" spans="1:12">
       <c r="A57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4760,7 +4810,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4775,12 +4825,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" ht="27" spans="1:12">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4798,7 +4848,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4813,12 +4863,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B59" t="s">
         <v>36</v>
@@ -4836,7 +4886,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4851,12 +4901,12 @@
         <v>39</v>
       </c>
       <c r="L59" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" ht="67.5" spans="1:12">
       <c r="A60" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4874,7 +4924,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4889,12 +4939,12 @@
         <v>43</v>
       </c>
       <c r="L60" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B61" t="s">
         <v>29</v>
@@ -4912,7 +4962,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4927,12 +4977,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" ht="69" spans="1:12">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4950,7 +5000,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -4965,12 +5015,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" ht="67.5" spans="1:12">
       <c r="A63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -4988,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5000,15 +5050,15 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L63" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64" ht="40.5" spans="1:12">
       <c r="A64" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5026,7 +5076,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5041,7 +5091,7 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" ht="40.5" spans="1:12">
@@ -5064,27 +5114,27 @@
         <v>15</v>
       </c>
       <c r="G65" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H65" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J65" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" t="s">
+        <v>15</v>
+      </c>
+      <c r="L65" t="s">
         <v>214</v>
-      </c>
-      <c r="H65" t="s">
-        <v>15</v>
-      </c>
-      <c r="I65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J65" t="s">
-        <v>15</v>
-      </c>
-      <c r="K65" t="s">
-        <v>15</v>
-      </c>
-      <c r="L65" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="66" ht="30" spans="1:12">
       <c r="A66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B66" t="s">
         <v>36</v>
@@ -5102,7 +5152,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5117,12 +5167,12 @@
         <v>39</v>
       </c>
       <c r="L66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" ht="54" spans="1:12">
       <c r="A67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5140,7 +5190,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5152,15 +5202,15 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L67" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68" ht="57" spans="1:12">
       <c r="A68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5178,7 +5228,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5193,12 +5243,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" ht="58.5" spans="1:12">
       <c r="A69" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5216,7 +5266,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5231,12 +5281,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70" ht="40.5" spans="1:12">
       <c r="A70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B70" t="s">
         <v>36</v>
@@ -5254,7 +5304,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5269,12 +5319,12 @@
         <v>39</v>
       </c>
       <c r="L70" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71" ht="40.5" spans="1:12">
       <c r="A71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5292,7 +5342,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5307,12 +5357,12 @@
         <v>43</v>
       </c>
       <c r="L71" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5330,7 +5380,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5345,12 +5395,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="73" ht="54" spans="1:12">
       <c r="A73" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B73" t="s">
         <v>36</v>
@@ -5368,7 +5418,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5383,12 +5433,12 @@
         <v>39</v>
       </c>
       <c r="L73" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74" ht="54" spans="1:12">
       <c r="A74" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5406,7 +5456,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5421,12 +5471,12 @@
         <v>43</v>
       </c>
       <c r="L74" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="75" ht="69" spans="1:12">
       <c r="A75" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5444,7 +5494,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5459,12 +5509,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" ht="67.5" spans="1:12">
       <c r="A76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5482,7 +5532,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5497,12 +5547,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" ht="40.5" spans="1:12">
       <c r="A77" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5520,7 +5570,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5532,15 +5582,15 @@
         <v>15</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L77" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="78" ht="90" spans="1:12">
       <c r="A78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5558,7 +5608,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5573,12 +5623,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79" ht="30" spans="1:12">
       <c r="A79" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B79" t="s">
         <v>36</v>
@@ -5596,7 +5646,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5608,10 +5658,10 @@
         <v>15</v>
       </c>
       <c r="K79" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -5632,39 +5682,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5672,7 +5722,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -5680,7 +5730,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5688,7 +5738,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B8" t="s">
         <v>100</v>
@@ -5696,7 +5746,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B9" t="s">
         <v>76</v>
@@ -5704,50 +5754,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -5769,616 +5819,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D13" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E15" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F15" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C16" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F16" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F17" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B18" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C18" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D18" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F18" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B20" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C20" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D20" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E20" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F20" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B21" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C21" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D21" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E21" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F21" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B22" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C22" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D22" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E22" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F22" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B23" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C23" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D23" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E23" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F23" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B24" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C24" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D24" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E24" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F24" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B25" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C25" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D25" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E25" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F25" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B26" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C26" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D26" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E26" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F26" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B27" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C27" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D27" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F27" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C28" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E28" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F28" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B29" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D29" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E29" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F29" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C30" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D30" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E30" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F30" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B31" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C31" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D31" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
